--- a/files/team-entry-13.xlsx
+++ b/files/team-entry-13.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C14"/>
+  <dimension ref="B2:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -642,7 +642,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>참가비</t>
@@ -666,7 +666,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>개인전</t>
@@ -678,7 +678,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2인전</t>
@@ -731,6 +731,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/files/team-entry-13.xlsx
+++ b/files/team-entry-13.xlsx
@@ -170,7 +170,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -286,11 +286,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -373,6 +374,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -762,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C15"/>
+  <dimension ref="B2:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -915,7 +920,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
@@ -931,12 +935,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C15"/>
+  <dimension ref="B2:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="2" ht="32" customHeight="1">
@@ -957,7 +961,7 @@
     <row r="5" ht="26" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>대표 지도자 성명</t>
+          <t>대표자 성명</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
@@ -1019,25 +1023,26 @@
     <row r="12" ht="26" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>보호자 동의 확인</t>
+          <t>보호자 동의 확인 여부(통합)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>작성일</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>※ 노란 칸은 자동 계산돼요. 입금은 확정 안내 문자를 받은 뒤 3일 안에 해 주세요.</t>
         </is>
       </c>
+      <c r="C13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>※ 보호자 동의여부를 포함한 단체 참여하는 과정에서의 책임 해당 단체에 있습니다. 이에 동의하고 대회에 참여합니다.</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
